--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488291_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488291_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. MOLINA LOPEZ</t>
+          <t>J. PINILLA NUNEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6167</v>
+        <v>8.459</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7661</v>
+        <v>2.9045</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8506</v>
+        <v>5.5545</v>
       </c>
       <c r="G2" t="n">
-        <v>1.552</v>
+        <v>4.6884</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7747000000000001</v>
+        <v>1.9928</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7773</v>
+        <v>2.6956</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1077</v>
+        <v>2.5064</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2322</v>
+        <v>1.1165</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1244</v>
+        <v>1.3899</v>
       </c>
       <c r="M2" t="n">
-        <v>1.6597</v>
+        <v>2.182</v>
       </c>
       <c r="N2" t="n">
-        <v>1.0069</v>
+        <v>0.8763</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6529</v>
+        <v>1.3057</v>
       </c>
       <c r="P2" t="n">
-        <v>2.594</v>
+        <v>2.9646</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.594</v>
+        <v>2.9646</v>
       </c>
       <c r="S2" t="n">
-        <v>1.638</v>
+        <v>0.4915</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3567</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2813</v>
+        <v>0.4079</v>
       </c>
       <c r="V2" t="n">
-        <v>2.8327</v>
+        <v>0.3144</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5172</v>
+        <v>0.3144</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PINILLA NUNEZ</t>
+          <t>M. MOLINA LOPEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.7188</v>
+        <v>7.9126</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1643</v>
+        <v>3.0374</v>
       </c>
       <c r="F3" t="n">
-        <v>5.5545</v>
+        <v>4.8752</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6884</v>
+        <v>1.552</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9928</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6956</v>
+        <v>0.7773</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5064</v>
+        <v>-0.1077</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1165</v>
+        <v>-0.2322</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3899</v>
+        <v>0.1244</v>
       </c>
       <c r="M3" t="n">
-        <v>2.182</v>
+        <v>1.6597</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8763</v>
+        <v>1.0069</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3057</v>
+        <v>0.6529</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9646</v>
+        <v>2.594</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9646</v>
+        <v>2.594</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2487</v>
+        <v>0.9339</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6566</v>
+        <v>0.628</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4079</v>
+        <v>0.3059</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3144</v>
+        <v>2.8327</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3144</v>
+        <v>2.5172</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.4291</v>
+        <v>6.9942</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1927</v>
+        <v>4.7578</v>
       </c>
       <c r="F4" t="n">
         <v>2.2364</v>
@@ -766,10 +766,10 @@
         <v>2.4087</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6552</v>
+        <v>1.2202</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4749</v>
+        <v>1.0399</v>
       </c>
       <c r="U4" t="n">
         <v>0.1803</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.2739</v>
+        <v>5.4932</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4301</v>
+        <v>1.8218</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8438</v>
+        <v>3.6715</v>
       </c>
       <c r="G5" t="n">
         <v>2.2278</v>
@@ -844,13 +844,13 @@
         <v>1.4823</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2281</v>
+        <v>1.4475</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4004</v>
+        <v>0.7921</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8277</v>
+        <v>0.6553</v>
       </c>
       <c r="V5" t="n">
         <v>1.4474</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.0089</v>
+        <v>4.3786</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7123</v>
+        <v>1.9836</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2965</v>
+        <v>2.395</v>
       </c>
       <c r="G6" t="n">
         <v>2.2614</v>
@@ -922,13 +922,13 @@
         <v>1.8529</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7442</v>
+        <v>2.114</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3466</v>
+        <v>1.6179</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3977</v>
+        <v>0.4961</v>
       </c>
       <c r="V6" t="n">
         <v>0.1886</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7741</v>
+        <v>4.1752</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8468</v>
+        <v>0.5789</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6209</v>
+        <v>3.5963</v>
       </c>
       <c r="G7" t="n">
         <v>2.4214</v>
@@ -1000,13 +1000,13 @@
         <v>2.7793</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4293</v>
+        <v>0.9718</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0.5926</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4039</v>
+        <v>0.3793</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0708</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5474</v>
+        <v>2.676</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2375</v>
+        <v>-1.1828</v>
       </c>
       <c r="F8" t="n">
-        <v>3.7849</v>
+        <v>3.8587</v>
       </c>
       <c r="G8" t="n">
         <v>3.0155</v>
@@ -1078,13 +1078,13 @@
         <v>2.7793</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1798</v>
+        <v>0.3084</v>
       </c>
       <c r="T8" t="n">
-        <v>0.051</v>
+        <v>0.1057</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1288</v>
+        <v>0.2027</v>
       </c>
       <c r="V8" t="n">
         <v>-1.5744</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5576</v>
+        <v>2.6611</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.105</v>
+        <v>0.6785</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6625</v>
+        <v>1.9826</v>
       </c>
       <c r="G9" t="n">
         <v>1.4113</v>
@@ -1156,13 +1156,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2243</v>
+        <v>0.8792</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3619</v>
+        <v>0.4216</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1375</v>
+        <v>0.4576</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. ÁLVAREZ GONZÁLEZ</t>
+          <t>J. RICARDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2441</v>
+        <v>1.5817</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2441</v>
+        <v>1.4882</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.0936</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2441</v>
+        <v>0.4382</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.6152</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2441</v>
+        <v>-0.177</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2441</v>
+        <v>1.5256</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1.503</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2441</v>
+        <v>0.0226</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-1.0874</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-0.8878</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.1996</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.2234</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.7561</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.5397</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.2164</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.9433</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.2022</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. RICARDO</t>
+          <t>C. ÁLVAREZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1298</v>
+        <v>1.2441</v>
       </c>
       <c r="E11" t="n">
-        <v>0.987</v>
+        <v>1.2441</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1428</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4382</v>
+        <v>1.2441</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6152</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.177</v>
+        <v>1.2441</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5256</v>
+        <v>1.2441</v>
       </c>
       <c r="K11" t="n">
-        <v>1.503</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0226</v>
+        <v>1.2441</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0874</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8878</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1996</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2234</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3042</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0386</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2656</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9433</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2022</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>C. ALVAREZ GONZALEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1218</v>
+        <v>-0.1591</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.2414</v>
+        <v>-1.9552</v>
       </c>
       <c r="F12" t="n">
-        <v>5.1196</v>
+        <v>1.7961</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.6047</v>
+        <v>-0.5896</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.7877</v>
+        <v>0.372</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1829</v>
+        <v>-0.9616</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.7371</v>
+        <v>-1.1584</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.9444</v>
+        <v>0.0644</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2074</v>
+        <v>-1.2228</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1323</v>
+        <v>0.5687</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1567</v>
+        <v>0.3076</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9756</v>
+        <v>0.2611</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.1853</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.891</v>
+        <v>-0.9264</v>
       </c>
       <c r="R12" t="n">
-        <v>3.3352</v>
+        <v>1.1117</v>
       </c>
       <c r="S12" t="n">
-        <v>4.4807</v>
+        <v>0.2453</v>
       </c>
       <c r="T12" t="n">
-        <v>3.7033</v>
+        <v>0.1296</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7774</v>
+        <v>0.1156</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.442</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3166</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. ALVAREZ GONZALEZ</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4036</v>
+        <v>-2.0947</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2489</v>
+        <v>-6.9927</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8453</v>
+        <v>4.898</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5896</v>
+        <v>-3.6047</v>
       </c>
       <c r="H13" t="n">
-        <v>0.372</v>
+        <v>-4.7877</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9616</v>
+        <v>1.1829</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.1584</v>
+        <v>-4.7371</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0644</v>
+        <v>-4.9444</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2228</v>
+        <v>0.2074</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5687</v>
+        <v>1.1323</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3076</v>
+        <v>0.1567</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2611</v>
+        <v>0.9756</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1853</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9264</v>
+        <v>-3.891</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1117</v>
+        <v>3.3352</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0007</v>
+        <v>2.5079</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1641</v>
+        <v>1.9521</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1649</v>
+        <v>0.5558</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.442</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.3166</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.1253</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>42.77500000000001</v>
+        <v>43.32189999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>7.816999999999999</v>
+        <v>8.364099999999997</v>
       </c>
       <c r="F14" t="n">
-        <v>34.95780000000001</v>
+        <v>34.9579</v>
       </c>
       <c r="G14" t="n">
         <v>18.7243</v>
@@ -1522,7 +1522,7 @@
         <v>8.681099999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>5.149799999999998</v>
+        <v>5.149799999999997</v>
       </c>
       <c r="L14" t="n">
         <v>3.531199999999999</v>
@@ -1546,13 +1546,13 @@
         <v>24.0873</v>
       </c>
       <c r="S14" t="n">
-        <v>11.3286</v>
+        <v>11.8758</v>
       </c>
       <c r="T14" t="n">
-        <v>7.3557</v>
+        <v>7.902799999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>3.973</v>
+        <v>3.9729</v>
       </c>
       <c r="V14" t="n">
         <v>3.4577</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2193</v>
+        <v>0.6964</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0378</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1815</v>
+        <v>1.3441</v>
       </c>
       <c r="G15" t="n">
         <v>2.0116</v>
@@ -1624,13 +1624,13 @@
         <v>1.1117</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5238</v>
+        <v>0.0009</v>
       </c>
       <c r="T15" t="n">
-        <v>0.965</v>
+        <v>0.2795</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4412</v>
+        <v>-0.2786</v>
       </c>
       <c r="V15" t="n">
         <v>2.2044</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.9262</v>
+        <v>-2.0761</v>
       </c>
       <c r="E16" t="n">
         <v>-1.5325</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3936</v>
+        <v>-0.5436</v>
       </c>
       <c r="G16" t="n">
         <v>-3.863</v>
@@ -1702,13 +1702,13 @@
         <v>2.4087</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0103</v>
+        <v>-1.1602</v>
       </c>
       <c r="T16" t="n">
         <v>-0.8157</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1945</v>
+        <v>-0.3445</v>
       </c>
       <c r="V16" t="n">
         <v>2.3913</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.5096</v>
+        <v>-3.257</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.8048</v>
+        <v>-3.609</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2952</v>
+        <v>0.3519</v>
       </c>
       <c r="G17" t="n">
         <v>-4.4209</v>
@@ -1780,13 +1780,13 @@
         <v>2.0382</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1274</v>
+        <v>-0.8748</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6479</v>
+        <v>-0.452</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4795</v>
+        <v>-0.4228</v>
       </c>
       <c r="V17" t="n">
         <v>0.0005</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.6485</v>
+        <v>-3.4767</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.9793</v>
+        <v>-3.8814</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3308</v>
+        <v>0.4047</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2143</v>
@@ -1858,13 +1858,13 @@
         <v>0.9264</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.953</v>
+        <v>-0.7813</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5471</v>
+        <v>-0.4492</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4059</v>
+        <v>-0.332</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6283</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. QUINTA RAMOS</t>
+          <t>S. VICENTE GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.0706</v>
+        <v>-5.9107</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.9093</v>
+        <v>-5.0526</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1613</v>
+        <v>-0.858</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8049</v>
+        <v>-2.551</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2687</v>
+        <v>-1.7844</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0736</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-2.9868</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3818</v>
+        <v>-1.091</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3057</v>
+        <v>-1.8958</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.881</v>
+        <v>0.4358</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1131</v>
+        <v>-0.6934</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7678</v>
+        <v>1.1292</v>
       </c>
       <c r="P19" t="n">
-        <v>-4.2616</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.5586</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>1.297</v>
+        <v>1.4823</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3104</v>
+        <v>-1.9014</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5733</v>
+        <v>-0.8244</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2629</v>
+        <v>-1.0769</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3144</v>
+        <v>-2.0142</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3144</v>
+        <v>-1.6992</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. VALDIVIA SANTILLANA</t>
+          <t>J. QUINTA RAMOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.8949</v>
+        <v>-6.0946</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.7998</v>
+        <v>-6.0072</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0951</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2302</v>
+        <v>-1.8049</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.453</v>
+        <v>0.2687</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2228</v>
+        <v>-2.0736</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.123</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4607</v>
+        <v>0.3818</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3378</v>
+        <v>-1.3057</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1072</v>
+        <v>-0.881</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9922</v>
+        <v>-0.1131</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.115</v>
+        <v>-0.7678</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.7793</v>
+        <v>-4.2616</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.6322</v>
+        <v>-5.5586</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8529</v>
+        <v>1.297</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.7607</v>
+        <v>0.2863</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3592</v>
+        <v>0.4754</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.4015</v>
+        <v>-0.189</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1248</v>
+        <v>-0.3144</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.4392</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. VICENTE GARCIA</t>
+          <t>F. VALDIVIA SANTILLANA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.9403</v>
+        <v>-6.2346</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.4443</v>
+        <v>-5.4081</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.496</v>
+        <v>-0.8265</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.551</v>
+        <v>-1.2302</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7844</v>
+        <v>-2.453</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7665999999999999</v>
+        <v>1.2228</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.9868</v>
+        <v>-0.123</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.091</v>
+        <v>-1.4607</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.8958</v>
+        <v>1.3378</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4358</v>
+        <v>-1.1072</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6934</v>
+        <v>-0.9922</v>
       </c>
       <c r="O21" t="n">
-        <v>1.1292</v>
+        <v>-0.115</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5558999999999999</v>
+        <v>-2.7793</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9264</v>
+        <v>-4.6322</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4823</v>
+        <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.931</v>
+        <v>-2.1003</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2162</v>
+        <v>-0.9674</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.7149</v>
+        <v>-1.1329</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.0142</v>
+        <v>-0.1248</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.315</v>
+        <v>0.3144</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.6992</v>
+        <v>-0.4392</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.022</v>
+        <v>-6.9144</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.9171</v>
+        <v>-6.2109</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1049</v>
+        <v>-0.7034</v>
       </c>
       <c r="G22" t="n">
         <v>-4.6781</v>
@@ -2170,13 +2170,13 @@
         <v>2.4087</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.533</v>
+        <v>-1.4254</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3444</v>
+        <v>-0.6382</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1886</v>
+        <v>-0.7872</v>
       </c>
       <c r="V22" t="n">
         <v>-0.4403</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.9821</v>
+        <v>-7.5486</v>
       </c>
       <c r="E23" t="n">
         <v>-2.6084</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.3737</v>
+        <v>-4.9402</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9734</v>
@@ -2248,13 +2248,13 @@
         <v>1.297</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8474</v>
+        <v>-1.4139</v>
       </c>
       <c r="T23" t="n">
         <v>-0.5807</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2667</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-4.5319</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-42.7749</v>
+        <v>-40.8163</v>
       </c>
       <c r="E24" t="n">
-        <v>-34.9577</v>
+        <v>-34.95780000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.817100000000001</v>
+        <v>-5.8584</v>
       </c>
       <c r="G24" t="n">
         <v>-18.7242</v>
       </c>
       <c r="H24" t="n">
-        <v>-8.356300000000001</v>
+        <v>-8.356299999999999</v>
       </c>
       <c r="I24" t="n">
         <v>-10.3679</v>
@@ -2326,13 +2326,13 @@
         <v>14.8229</v>
       </c>
       <c r="S24" t="n">
-        <v>-11.3286</v>
+        <v>-9.370099999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.9729</v>
+        <v>-3.9727</v>
       </c>
       <c r="U24" t="n">
-        <v>-7.3557</v>
+        <v>-5.3971</v>
       </c>
       <c r="V24" t="n">
         <v>-3.4577</v>
@@ -2341,7 +2341,7 @@
         <v>3.1455</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.603199999999999</v>
+        <v>-6.603200000000001</v>
       </c>
     </row>
   </sheetData>
